--- a/web-output/output.xlsx
+++ b/web-output/output.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\TELKOM\MAGANG\Pos Indonesia\document-hub-penilaian-gcg\web-output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B58FCE6-0FB8-4CB5-BA8D-B477DCCBC872}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BCFE991-3FD1-416D-B9D1-5FE1E0E003B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21458,7 +21458,7 @@
         <v>100</v>
       </c>
       <c r="H570" s="42">
-        <v>87.451700000000002</v>
+        <v>99</v>
       </c>
       <c r="I570" s="12"/>
       <c r="J570" s="35" t="s">

--- a/web-output/output.xlsx
+++ b/web-output/output.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\TELKOM\MAGANG\Pos Indonesia\document-hub-penilaian-gcg\web-output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BCFE991-3FD1-416D-B9D1-5FE1E0E003B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AAD272B-C702-4B26-AE6A-D897E81365A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5676" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cleaned Data" sheetId="1" r:id="rId1"/>
@@ -20831,7 +20831,7 @@
         <v>100</v>
       </c>
       <c r="H551" s="42">
-        <v>87.451700000000002</v>
+        <v>100</v>
       </c>
       <c r="I551" s="12"/>
       <c r="J551" s="35" t="s">
@@ -21458,7 +21458,7 @@
         <v>100</v>
       </c>
       <c r="H570" s="42">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I570" s="12"/>
       <c r="J570" s="35" t="s">
